--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -1995,7 +1995,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16662,7 +16662,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18639,7 +18639,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -18878,7 +18878,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20764,7 +20764,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -21003,7 +21003,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -1995,7 +1995,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16662,7 +16662,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18639,7 +18639,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -18878,7 +18878,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -20764,7 +20764,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -21003,7 +21003,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -21093,6 +21093,154 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21126,7 +21274,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -21209,7 +21357,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -21219,7 +21367,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -1751,9 +1751,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2005,7 +2002,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2244,7 +2241,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -4111,7 +4108,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4341,7 +4338,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -4571,7 +4568,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -4714,9 +4711,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4968,7 +4962,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5207,7 +5201,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6926,7 +6920,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -7156,7 +7150,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -7386,7 +7380,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -7529,9 +7523,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -7783,7 +7774,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8022,7 +8013,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -9506,9 +9497,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -9889,7 +9877,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -10119,7 +10107,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -10349,7 +10337,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -10492,9 +10480,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -10746,7 +10731,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -10985,7 +10970,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12321,9 +12306,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -12704,7 +12686,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -12934,7 +12916,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -13164,7 +13146,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -13307,9 +13289,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -13561,7 +13540,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -13800,7 +13779,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15432,9 +15411,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -15815,7 +15791,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -16045,7 +16021,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -16275,7 +16251,7 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -16418,9 +16394,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -16672,7 +16645,7 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN92" t="b">
@@ -16911,7 +16884,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -17063,9 +17036,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -17211,9 +17181,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -17359,9 +17326,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -17507,9 +17471,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -17655,9 +17616,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -17803,9 +17761,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -17951,9 +17906,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -18099,9 +18051,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -18247,9 +18196,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -18395,9 +18341,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -18649,7 +18592,7 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -18888,7 +18831,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -19040,9 +18983,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -19188,9 +19128,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -19336,9 +19273,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -19484,9 +19418,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -19632,9 +19563,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -19780,9 +19708,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -19928,9 +19853,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -20076,9 +19998,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -20224,9 +20143,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -20372,9 +20288,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20520,9 +20433,6 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0</v>
       </c>
@@ -20774,7 +20684,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -21013,7 +20923,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -21163,9 +21073,6 @@
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -21148,6 +21148,151 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21181,7 +21326,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21409,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -21274,7 +21419,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -18297,12 +18297,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -18336,100 +18336,84 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O103" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>0.0005662056925550997</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18440,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -18505,98 +18489,23 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>동물인플루엔자 인체감염증</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD104" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE104" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF104" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG104" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN104" t="b">
-        <v>1</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -18746,12 +18655,12 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
@@ -18761,7 +18670,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>신종인플루엔자</t>
+          <t>동물인플루엔자 인체감염증</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -18826,7 +18735,7 @@
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Korea KDCA novel influenza category.</t>
+          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
@@ -18835,7 +18744,7 @@
         </is>
       </c>
       <c r="AN105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -18934,17 +18843,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -18969,7 +18878,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -18983,76 +18892,170 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>신종인플루엔자</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Korea KDCA novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN106" t="b">
+        <v>0</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19084,12 +19087,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -19162,42 +19165,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19229,12 +19232,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -19259,7 +19262,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -19307,42 +19310,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19374,12 +19377,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -19452,42 +19455,42 @@
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19519,12 +19522,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -19549,7 +19552,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -19597,42 +19600,42 @@
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19664,12 +19667,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -19742,42 +19745,42 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19809,12 +19812,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -19839,7 +19842,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -19887,42 +19890,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19954,12 +19957,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -20032,42 +20035,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20099,12 +20102,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -20129,7 +20132,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -20177,42 +20180,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20244,12 +20247,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -20274,12 +20277,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N115" t="n">
@@ -20322,42 +20325,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20389,12 +20392,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20441,87 +20444,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
-      <c r="AA116" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20548,7 +20532,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -20597,98 +20581,23 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>동물인플루엔자 인체감염증</t>
-        </is>
-      </c>
-      <c r="Y117" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD117" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE117" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF117" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG117" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN117" t="b">
-        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -20838,12 +20747,12 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
@@ -20853,7 +20762,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>신종인플루엔자</t>
+          <t>동물인플루엔자 인체감염증</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -20918,7 +20827,7 @@
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Korea KDCA novel influenza category.</t>
+          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
@@ -20927,7 +20836,7 @@
         </is>
       </c>
       <c r="AN118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -21026,17 +20935,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21061,7 +20970,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -21075,76 +20984,170 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>신종인플루엔자</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Korea KDCA novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN119" t="b">
+        <v>0</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -21206,7 +21209,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -21288,6 +21291,151 @@
         </is>
       </c>
       <c r="BC120" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -21409,7 +21557,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -21419,7 +21567,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -21471,7 +21619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -21441,6 +21441,151 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21474,7 +21619,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -21557,7 +21702,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -21567,7 +21712,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16082,7 +16082,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20467,7 +20467,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -25303,7 +25303,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -25542,7 +25542,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28974,7 +28974,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -29213,7 +29213,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -32642,7 +32642,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -32881,7 +32881,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16082,7 +16082,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20467,7 +20467,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -25303,7 +25303,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -25542,7 +25542,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28974,7 +28974,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -29213,7 +29213,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -32642,7 +32642,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -32881,7 +32881,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -28684,17 +28684,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -28733,17 +28733,34 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="R156" t="n">
-        <v>0</v>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_HK_NOVEL_INFLUENZA_H5</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>SER_HK_NOVEL_INFLUENZA_H5</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>SRC_HK_CHP</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Influenza A - Influenza A (H5)</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -28751,77 +28768,126 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>country:HK:national</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>HK_CHP_H5_current</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP H5 novel influenza A category.</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN156" t="b">
+        <v>0</v>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>no_eligible_public_projection</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -28853,12 +28919,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -28899,22 +28965,22 @@
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_HK_NOVEL_INFLUENZA_H7</t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_HK_NOVEL_INFLUENZA_H7</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_HK_CHP</t>
         </is>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>동물인플루엔자 인체감염증</t>
+          <t>Influenza A - Influenza A (H7)</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
@@ -28939,7 +29005,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:HK:national</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr">
@@ -28949,12 +29015,12 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG157" t="inlineStr">
@@ -28974,12 +29040,12 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>HK_CHP_H7_current</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+          <t>Hong Kong, China CHP H7 novel influenza A category.</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
@@ -28988,79 +29054,70 @@
         </is>
       </c>
       <c r="AN157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>no_eligible_public_projection</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -29092,12 +29149,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -29138,22 +29195,22 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
+          <t>SER_HK_NOVEL_INFLUENZA_OTHERS</t>
         </is>
       </c>
       <c r="V158" t="inlineStr">
         <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
+          <t>SER_HK_NOVEL_INFLUENZA_OTHERS</t>
         </is>
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_HK_CHP</t>
         </is>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>신종인플루엔자</t>
+          <t>Novel influenza A infection - Others</t>
         </is>
       </c>
       <c r="Y158" t="inlineStr">
@@ -29178,7 +29235,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:HK:national</t>
         </is>
       </c>
       <c r="AD158" t="inlineStr">
@@ -29188,12 +29245,12 @@
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG158" t="inlineStr">
@@ -29213,12 +29270,12 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>HK_CHP_other_current</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>Korea KDCA novel influenza category.</t>
+          <t>Hong Kong, China CHP residual novel influenza A category.</t>
         </is>
       </c>
       <c r="AM158" t="inlineStr">
@@ -29231,75 +29288,66 @@
       </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>no_eligible_public_projection</t>
         </is>
       </c>
       <c r="AQ158" t="inlineStr">
         <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -29331,12 +29379,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -29361,7 +29409,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -29383,68 +29431,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -29471,17 +29538,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -29506,7 +29573,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -29520,76 +29587,170 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>동물인플루엔자 인체감염증</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN160" t="b">
+        <v>1</v>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR160" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -29616,17 +29777,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -29651,7 +29812,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -29665,21 +29826,98 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="P161" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>신종인플루엔자</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD161" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE161" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG161" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH161" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI161" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>Korea KDCA novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM161" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN161" t="b">
+        <v>0</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
@@ -29688,7 +29926,7 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ161" t="inlineStr">
@@ -29696,9 +29934,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="AT161" t="n">
@@ -29706,47 +29949,47 @@
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -29773,17 +30016,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -29808,7 +30051,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -29822,168 +30065,76 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="P162" t="n">
-        <v>0</v>
-      </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>1</v>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30015,12 +30166,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -30045,7 +30196,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -30093,42 +30244,42 @@
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30160,12 +30311,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -30190,7 +30341,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -30204,6 +30355,9 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -30212,68 +30366,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
       <c r="AT164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30300,7 +30463,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -30335,7 +30498,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -30352,18 +30515,98 @@
       <c r="P165" t="n">
         <v>0</v>
       </c>
-      <c r="R165" t="n">
-        <v>0</v>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD165" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE165" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF165" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG165" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH165" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI165" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM165" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN165" t="b">
+        <v>1</v>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
@@ -30457,17 +30700,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -30492,7 +30735,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -30506,168 +30749,76 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="P166" t="n">
-        <v>0</v>
-      </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA166" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE166" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG166" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN166" t="b">
-        <v>1</v>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ166" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30699,12 +30850,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -30729,7 +30880,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -30777,42 +30928,42 @@
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30844,12 +30995,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -30874,7 +31025,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -30888,6 +31039,9 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
@@ -30896,68 +31050,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
       <c r="AT168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30984,7 +31147,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -31019,7 +31182,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -31036,18 +31199,98 @@
       <c r="P169" t="n">
         <v>0</v>
       </c>
-      <c r="R169" t="n">
-        <v>0</v>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
@@ -31141,17 +31384,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -31176,7 +31419,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -31190,168 +31433,76 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="P170" t="n">
-        <v>0</v>
-      </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X170" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE170" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF170" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG170" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN170" t="b">
-        <v>1</v>
+      <c r="R170" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31383,12 +31534,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -31413,7 +31564,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -31461,42 +31612,42 @@
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31528,12 +31679,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -31558,7 +31709,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -31572,6 +31723,9 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -31580,68 +31734,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
       <c r="AT172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -31668,17 +31831,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -31703,7 +31866,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -31717,76 +31880,168 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="R173" t="n">
-        <v>0</v>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -31818,12 +32073,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -31848,7 +32103,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -31862,9 +32117,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="P174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -31873,77 +32125,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31970,17 +32213,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -32005,7 +32248,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -32019,168 +32262,76 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="P175" t="n">
-        <v>0</v>
-      </c>
-      <c r="U175" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>Avian Influenza</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA175" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD175" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE175" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF175" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG175" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN175" t="b">
-        <v>1</v>
+      <c r="R175" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32212,12 +32363,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -32242,12 +32393,12 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N176" t="n">
@@ -32290,42 +32441,42 @@
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32357,12 +32508,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -32387,12 +32538,12 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N177" t="n">
@@ -32401,6 +32552,9 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -32409,14 +32563,9 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -32426,7 +32575,7 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
@@ -32434,14 +32583,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="AT177" t="n">
@@ -32449,47 +32593,47 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32521,12 +32665,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -32551,12 +32695,12 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N178" t="n">
@@ -32565,24 +32709,27 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="V178" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>동물인플루엔자 인체감염증</t>
+          <t>Avian Influenza</t>
         </is>
       </c>
       <c r="Y178" t="inlineStr">
@@ -32592,12 +32739,12 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
@@ -32607,7 +32754,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD178" t="inlineStr">
@@ -32617,12 +32764,12 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>exact</t>
+          <t>narrower</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG178" t="inlineStr">
@@ -32642,12 +32789,12 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
         <is>
-          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM178" t="inlineStr">
@@ -32665,7 +32812,7 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ178" t="inlineStr">
@@ -32673,14 +32820,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS178" t="inlineStr">
         <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
         </is>
       </c>
       <c r="AT178" t="n">
@@ -32688,47 +32830,47 @@
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -32755,17 +32897,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -32804,170 +32946,76 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>SER_KR_NOVEL_INFLUENZA</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>SRC_KR_KDCA</t>
-        </is>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>신종인플루엔자</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>country:KR:national</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr">
+      <c r="R179" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr"/>
+      <c r="AT179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV179" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE179" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF179" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG179" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>Korea KDCA novel influenza category.</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN179" t="b">
-        <v>0</v>
-      </c>
-      <c r="AO179" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP179" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ179" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr">
-        <is>
-          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
-        </is>
-      </c>
-      <c r="AT179" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV179" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -32999,12 +33047,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -33029,7 +33077,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -33051,68 +33099,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR180" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
       <c r="AT180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -33139,17 +33206,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -33174,7 +33241,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -33188,21 +33255,98 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="P181" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" t="n">
-        <v>0</v>
-      </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>동물인플루엔자 인체감염증</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Korea KDCA animal influenza infection in humans, retained separately from the generic novel influenza category.</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN181" t="b">
+        <v>1</v>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
@@ -33211,7 +33355,7 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
@@ -33219,9 +33363,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS181" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="AT181" t="n">
@@ -33229,47 +33378,47 @@
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -33301,12 +33450,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -33331,7 +33480,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -33345,27 +33494,24 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="P182" t="n">
-        <v>0</v>
-      </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
         </is>
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+          <t>SER_KR_NOVEL_INFLUENZA</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>Avian Influenza</t>
+          <t>신종인플루엔자</t>
         </is>
       </c>
       <c r="Y182" t="inlineStr">
@@ -33375,12 +33521,12 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
@@ -33390,7 +33536,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr">
@@ -33400,12 +33546,12 @@
       </c>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>narrower</t>
+          <t>exact</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG182" t="inlineStr">
@@ -33425,12 +33571,12 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Korea KDCA novel influenza category.</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
@@ -33439,7 +33585,7 @@
         </is>
       </c>
       <c r="AN182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
@@ -33448,7 +33594,7 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
@@ -33456,9 +33602,14 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+          <t>SER_KR_ANIMAL_INFLUENZA_HUMAN_INFECTION</t>
         </is>
       </c>
       <c r="AT182" t="n">
@@ -33466,47 +33617,47 @@
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -33568,7 +33719,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -33713,7 +33864,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -33870,7 +34021,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -34107,7 +34258,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -34252,7 +34403,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -34409,7 +34560,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -34616,12 +34767,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -34646,7 +34797,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -34655,13 +34806,13 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
@@ -34694,40 +34845,579 @@
       </c>
       <c r="AV189" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA189" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB189" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC189" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT190" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV190" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC190" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Avian Influenza</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD191" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF191" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG191" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM191" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN191" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP191" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_AVIAN_INFLUENZA; SER_SG_HIST_AVIAN_INFLUENZA</t>
+        </is>
+      </c>
+      <c r="AT191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU191" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV191" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA191" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB191" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC191" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>novel-influenza-a</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>D016</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Novel influenza A</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>人感染新亚型流感</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>2</v>
+      </c>
+      <c r="O192" t="n">
+        <v>2</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr"/>
+      <c r="AT192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV192" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW189" t="inlineStr">
+      <c r="AW192" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX189" t="inlineStr">
+      <c r="AX192" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY189" t="inlineStr">
+      <c r="AY192" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ189" t="inlineStr">
+      <c r="AZ192" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA189" t="inlineStr">
+      <c r="BA192" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB189" t="inlineStr">
+      <c r="BB192" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC189" t="inlineStr">
+      <c r="BC192" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -34859,7 +35549,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
@@ -34879,7 +35569,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d016/2026-2029.xlsx
+++ b/diseases/d016/2026-2029.xlsx
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -16082,7 +16082,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -20467,7 +20467,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -25303,7 +25303,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -25542,7 +25542,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -29664,7 +29664,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -29903,7 +29903,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33332,7 +33332,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -33571,7 +33571,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
